--- a/database/controller_excel/Resguardo_Freddy_Arturo_Flores.xlsx
+++ b/database/controller_excel/Resguardo_Freddy_Arturo_Flores.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>20/05/2025</t>
+    <t>02/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Tampico</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
+    <t>Rednar García Harcía</t>
+  </si>
+  <si>
+    <t>Auxiliar Predictivo</t>
   </si>
 </sst>
 </file>
